--- a/Raw Materials/Extrusion/압출공정_제약조건.xlsx
+++ b/Raw Materials/Extrusion/압출공정_제약조건.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SWI\통합계획\클로드\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Check_In_Service\Extrusion_Vulcanization_Scheduling_System\Raw Materials\Extrusion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF085F71-6CA4-4D5B-8DA1-B95C81E3BC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{376E3DED-8989-4AB1-A98B-598DAF69A85F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="69">
   <si>
     <t>HOSE</t>
   </si>
@@ -130,9 +129,6 @@
   </si>
   <si>
     <t>A6722031002</t>
-  </si>
-  <si>
-    <t>25475-07201-1</t>
   </si>
   <si>
     <t>25482-07TA0</t>
@@ -237,13 +233,21 @@
   </si>
   <si>
     <t>후반근무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25474-2S010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25475-07201</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -618,11 +622,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059E7228-FCF1-46A2-AA33-DB251AF9E5B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.875" bestFit="1" customWidth="1"/>
@@ -648,7 +652,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -657,13 +661,13 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -732,7 +736,7 @@
       </c>
       <c r="K3" s="1"/>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -768,10 +772,10 @@
       </c>
       <c r="K4" s="1"/>
       <c r="N4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -810,10 +814,10 @@
       </c>
       <c r="K5" s="1"/>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P5">
         <v>4</v>
@@ -852,10 +856,10 @@
       </c>
       <c r="K6" s="1"/>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P6">
         <v>4.5</v>
@@ -894,10 +898,10 @@
       </c>
       <c r="K7" s="1"/>
       <c r="N7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P7">
         <v>5</v>
@@ -1544,7 +1548,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1">
         <v>9</v>
@@ -1579,7 +1583,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1">
         <v>9</v>
@@ -1614,7 +1618,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1">
         <v>9</v>
@@ -1649,7 +1653,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1">
         <v>9</v>
@@ -1684,7 +1688,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1">
         <v>11</v>
@@ -1719,7 +1723,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1">
         <v>11</v>
@@ -1754,31 +1758,31 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B33" s="1">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="C33" s="1">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="D33" s="1">
         <v>4.2</v>
       </c>
       <c r="E33" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33" s="1">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" s="1">
-        <v>430</v>
+        <v>275</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>9</v>
@@ -1789,7 +1793,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1">
         <v>13.5</v>
@@ -1807,13 +1811,13 @@
         <v>4.5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H34" s="1">
         <v>2</v>
       </c>
       <c r="I34" s="1">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>9</v>
@@ -1824,7 +1828,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1">
         <v>13.5</v>
@@ -1833,7 +1837,7 @@
         <v>12</v>
       </c>
       <c r="D35" s="1">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="E35" s="1">
         <v>7</v>
@@ -1842,13 +1846,13 @@
         <v>4.5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
       </c>
       <c r="I35" s="1">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>9</v>
@@ -1859,7 +1863,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1">
         <v>13.5</v>
@@ -1877,13 +1881,13 @@
         <v>4.5</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>9</v>
@@ -1894,7 +1898,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1">
         <v>13.5</v>
@@ -1912,13 +1916,13 @@
         <v>4.5</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H37" s="1">
         <v>2</v>
       </c>
       <c r="I37" s="1">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>9</v>
@@ -1929,40 +1933,42 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="C38" s="1">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="E38" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="1">
-        <v>700</v>
+        <v>395</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K38" s="1"/>
+      <c r="K38" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1">
         <v>18</v>
@@ -1980,13 +1986,13 @@
         <v>4</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>490</v>
+        <v>700</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>9</v>
@@ -1995,7 +2001,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1">
         <v>18</v>
@@ -2013,7 +2019,7 @@
         <v>4</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
@@ -2028,7 +2034,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1">
         <v>18</v>
@@ -2046,13 +2052,13 @@
         <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H41" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>590</v>
+        <v>490</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>9</v>
@@ -2061,7 +2067,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42" s="1">
         <v>18</v>
@@ -2070,7 +2076,7 @@
         <v>15.5</v>
       </c>
       <c r="D42" s="1">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="E42" s="1">
         <v>8</v>
@@ -2079,13 +2085,13 @@
         <v>4</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H42" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I42" s="1">
-        <v>520</v>
+        <v>590</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>9</v>
@@ -2094,7 +2100,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" s="1">
         <v>18</v>
@@ -2112,13 +2118,13 @@
         <v>4</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H43" s="1">
         <v>2</v>
       </c>
       <c r="I43" s="1">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="J43" s="1" t="s">
         <v>9</v>
@@ -2127,7 +2133,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1">
         <v>18</v>
@@ -2145,13 +2151,13 @@
         <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="1">
-        <v>560</v>
+        <v>450</v>
       </c>
       <c r="J44" s="1" t="s">
         <v>9</v>
@@ -2160,7 +2166,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B45" s="1">
         <v>18</v>
@@ -2178,13 +2184,13 @@
         <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H45" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="1">
-        <v>355</v>
+        <v>560</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>9</v>
@@ -2193,7 +2199,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" s="1">
         <v>18</v>
@@ -2211,13 +2217,13 @@
         <v>4</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="1">
-        <v>705</v>
+        <v>355</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>9</v>
@@ -2226,7 +2232,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B47" s="1">
         <v>18</v>
@@ -2234,8 +2240,8 @@
       <c r="C47" s="1">
         <v>15.5</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>58</v>
+      <c r="D47" s="1">
+        <v>4.2</v>
       </c>
       <c r="E47" s="1">
         <v>8</v>
@@ -2244,18 +2250,51 @@
         <v>4</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H47" s="1">
         <v>1</v>
       </c>
       <c r="I47" s="1">
+        <v>705</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K47" s="1"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1">
+        <v>18</v>
+      </c>
+      <c r="C48" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8</v>
+      </c>
+      <c r="F48" s="1">
+        <v>4</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
         <v>355</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K47" s="1"/>
+      <c r="J48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
